--- a/AtchisonRegime/Outputs/Brazil/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Brazil/MSCI_Europe/df_regSettingsMSCI_Europe.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10521,7 +10521,7 @@
         <v>-1.106168929183249</v>
       </c>
       <c r="C306" t="n">
-        <v>0.07010286730686353</v>
+        <v>0.08584304244701514</v>
       </c>
       <c r="D306" t="b">
         <v>0</v>
@@ -10554,7 +10554,7 @@
         <v>-1.023152096709701</v>
       </c>
       <c r="C307" t="n">
-        <v>0.06777076014117203</v>
+        <v>0.07461153673370037</v>
       </c>
       <c r="D307" t="b">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>-0.8887081705708955</v>
       </c>
       <c r="C308" t="n">
-        <v>0.08108255332278663</v>
+        <v>0.07532937712790448</v>
       </c>
       <c r="D308" t="b">
         <v>0</v>
@@ -10620,7 +10620,7 @@
         <v>-0.8060211384898766</v>
       </c>
       <c r="C309" t="n">
-        <v>0.03461839485758089</v>
+        <v>0.03958576536912412</v>
       </c>
       <c r="D309" t="b">
         <v>0</v>
@@ -10653,7 +10653,7 @@
         <v>-0.7401941763003826</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.0362272390278989</v>
+        <v>-0.03478208068685314</v>
       </c>
       <c r="D310" t="b">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>-0.6714028499367534</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.1204405614412703</v>
+        <v>-0.1167003150752939</v>
       </c>
       <c r="D311" t="b">
         <v>0</v>
@@ -10719,7 +10719,7 @@
         <v>-0.5590277466514001</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.1675986740596273</v>
+        <v>-0.1715903141306255</v>
       </c>
       <c r="D312" t="b">
         <v>0</v>
@@ -10752,7 +10752,7 @@
         <v>-0.4698383242787347</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.1760527105930659</v>
+        <v>-0.1828161926752659</v>
       </c>
       <c r="D313" t="b">
         <v>0</v>
@@ -10785,7 +10785,7 @@
         <v>-0.449811882553294</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.1470744605152078</v>
+        <v>-0.1566516972167822</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
@@ -10818,7 +10818,7 @@
         <v>-0.3853200776072436</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.08209173015700538</v>
+        <v>-0.09485529935348186</v>
       </c>
       <c r="D315" t="b">
         <v>0</v>
@@ -10848,10 +10848,10 @@
         <v>45747</v>
       </c>
       <c r="B316" t="n">
-        <v>-0.3084661278453371</v>
+        <v>-0.253891578687139</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.02718857488385517</v>
+        <v>-0.04580605020778437</v>
       </c>
       <c r="D316" t="b">
         <v>0</v>
@@ -10871,6 +10871,39 @@
         </is>
       </c>
       <c r="I316" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B317" t="n">
+        <v>-0.05005178341911259</v>
+      </c>
+      <c r="C317" t="n">
+        <v>-0.02169872933148871</v>
+      </c>
+      <c r="D317" t="b">
+        <v>0</v>
+      </c>
+      <c r="E317" t="b">
+        <v>0</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="G317" t="n">
+        <v>325618.0893537902</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
         <is>
           <t>Type 3</t>
         </is>
